--- a/SGC-CKN/Excel/c3c3af2e-87f0-484a-9366-2ab8c637585d_Bảng_kiểm_tra_công_tác_khoan_tạo_lỗ_cọc_khoan_nhồi_đại_trà_P14-25_D800_30-03-2026.xlsx
+++ b/SGC-CKN/Excel/c3c3af2e-87f0-484a-9366-2ab8c637585d_Bảng_kiểm_tra_công_tác_khoan_tạo_lỗ_cọc_khoan_nhồi_đại_trà_P14-25_D800_30-03-2026.xlsx
@@ -98,11 +98,11 @@
     <t>Sét pha, xám nâu, TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">17:10
+    <t xml:space="preserve">14:10
 30/3/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">17:15
+    <t xml:space="preserve">14:15
 30/3/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
   </si>
   <si>
-    <t xml:space="preserve">17:20
+    <t xml:space="preserve">14:20
 30/3/2026</t>
   </si>
   <si>
@@ -128,7 +128,7 @@
     <t>Sét- đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
   </si>
   <si>
-    <t xml:space="preserve">17:50
+    <t xml:space="preserve">14:30
 30/3/2026</t>
   </si>
   <si>
@@ -138,7 +138,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">18:50
+    <t xml:space="preserve">14:50
 30/3/2026</t>
   </si>
   <si>
@@ -148,7 +148,7 @@
     <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
   </si>
   <si>
-    <t xml:space="preserve">19:10
+    <t xml:space="preserve">15:10
 30/3/2026</t>
   </si>
   <si>
@@ -158,7 +158,7 @@
     <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">19:30
+    <t xml:space="preserve">15:30
 30/3/2026</t>
   </si>
   <si>
@@ -168,7 +168,7 @@
     <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ kẹp hạt cát nhỏ, bụi</t>
   </si>
   <si>
-    <t xml:space="preserve">19:57
+    <t xml:space="preserve">16:37
 30/3/2026</t>
   </si>
   <si>
@@ -299,7 +299,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -359,6 +359,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -459,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -539,22 +544,25 @@
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1140,7 +1148,7 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-0.71</v>
+        <v>-0.01</v>
       </c>
       <c r="G11" s="5">
         <v>-2.71</v>
@@ -1149,10 +1157,10 @@
         <v>0.08</v>
       </c>
       <c r="I11" s="5">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J11" s="8">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1213,16 +1221,16 @@
         <v>-12.91</v>
       </c>
       <c r="G13" s="12">
-        <v>-23.11</v>
+        <v>-18.11</v>
       </c>
       <c r="H13" s="12">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I13" s="12">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="J13" s="8">
-        <v>20.4</v>
+        <v>31.2</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>34</v>
@@ -1245,19 +1253,19 @@
         <v>40</v>
       </c>
       <c r="F14" s="15">
-        <v>-23.11</v>
+        <v>-18.11</v>
       </c>
       <c r="G14" s="15">
         <v>-28.8</v>
       </c>
       <c r="H14" s="15">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="I14" s="15">
-        <v>5.69</v>
+        <v>10.69</v>
       </c>
       <c r="J14" s="8">
-        <v>5.69</v>
+        <v>32.07</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>34</v>
@@ -1318,16 +1326,16 @@
         <v>-35.61</v>
       </c>
       <c r="G16" s="21">
-        <v>-38.41</v>
+        <v>-38.1</v>
       </c>
       <c r="H16" s="21">
         <v>0.33</v>
       </c>
       <c r="I16" s="21">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="J16" s="8">
-        <v>8.4</v>
+        <v>7.47</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>34</v>
@@ -1350,73 +1358,73 @@
         <v>49</v>
       </c>
       <c r="F17" s="24">
-        <v>-38.41</v>
+        <v>-38.1</v>
       </c>
       <c r="G17" s="24">
         <v>-43.2</v>
       </c>
       <c r="H17" s="24">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="I17" s="24">
-        <v>4.79</v>
-      </c>
-      <c r="J17" s="8">
-        <v>10.64</v>
+        <v>5.1</v>
+      </c>
+      <c r="J17" s="27">
+        <v>4.57</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <v>-43.2</v>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="28">
         <v>-49.8</v>
       </c>
-      <c r="H18" s="27">
-        <v>0.08</v>
-      </c>
-      <c r="I18" s="27">
+      <c r="H18" s="28">
+        <v>3.42</v>
+      </c>
+      <c r="I18" s="28">
         <v>6.6</v>
       </c>
-      <c r="J18" s="8">
-        <v>79.2</v>
-      </c>
-      <c r="K18" s="28" t="s">
+      <c r="J18" s="27">
+        <v>1.93</v>
+      </c>
+      <c r="K18" s="29" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="30"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="31"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1552,7 +1560,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-0.71</v>
+        <v>-0.01</v>
       </c>
       <c r="F2" s="5">
         <v>-2.71</v>
@@ -1561,10 +1569,10 @@
         <v>0.08</v>
       </c>
       <c r="H2" s="5">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="I2" s="8">
-        <v>24</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1613,16 +1621,16 @@
         <v>-12.91</v>
       </c>
       <c r="F4" s="12">
-        <v>-23.11</v>
+        <v>-18.11</v>
       </c>
       <c r="G4" s="12">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H4" s="12">
-        <v>10.2</v>
+        <v>5.2</v>
       </c>
       <c r="I4" s="8">
-        <v>20.4</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1639,19 +1647,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-23.11</v>
+        <v>-18.11</v>
       </c>
       <c r="F5" s="15">
         <v>-28.8</v>
       </c>
       <c r="G5" s="15">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="H5" s="15">
-        <v>5.69</v>
+        <v>10.69</v>
       </c>
       <c r="I5" s="8">
-        <v>5.69</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1700,16 +1708,16 @@
         <v>-35.61</v>
       </c>
       <c r="F7" s="21">
-        <v>-38.41</v>
+        <v>-38.1</v>
       </c>
       <c r="G7" s="21">
         <v>0.33</v>
       </c>
       <c r="H7" s="21">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="I7" s="8">
-        <v>8.4</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1726,77 +1734,77 @@
         <v>1</v>
       </c>
       <c r="E8" s="24">
-        <v>-38.41</v>
+        <v>-38.1</v>
       </c>
       <c r="F8" s="24">
         <v>-43.2</v>
       </c>
       <c r="G8" s="24">
-        <v>0.45</v>
+        <v>1.12</v>
       </c>
       <c r="H8" s="24">
-        <v>4.79</v>
-      </c>
-      <c r="I8" s="8">
-        <v>10.64</v>
+        <v>5.1</v>
+      </c>
+      <c r="I8" s="27">
+        <v>4.57</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="27">
+      <c r="A9" s="28">
         <v>8</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="28">
         <v>1</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="28">
         <v>-43.2</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <v>-49.8</v>
       </c>
-      <c r="G9" s="27">
-        <v>0.08</v>
-      </c>
-      <c r="H9" s="27">
+      <c r="G9" s="28">
+        <v>3.42</v>
+      </c>
+      <c r="H9" s="28">
         <v>6.6</v>
       </c>
-      <c r="I9" s="8">
-        <v>79.2</v>
+      <c r="I9" s="27">
+        <v>1.93</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="33">
         <v>8</v>
       </c>
-      <c r="E10" s="32">
-        <v>-0.71</v>
-      </c>
-      <c r="F10" s="32">
+      <c r="E10" s="33">
+        <v>-0.01</v>
+      </c>
+      <c r="F10" s="33">
         <v>-49.8</v>
       </c>
-      <c r="G10" s="32">
-        <v>2.87</v>
-      </c>
-      <c r="H10" s="32">
-        <v>49.09</v>
-      </c>
-      <c r="I10" s="32">
-        <v>17.12</v>
+      <c r="G10" s="33">
+        <v>5.87</v>
+      </c>
+      <c r="H10" s="33">
+        <v>49.79</v>
+      </c>
+      <c r="I10" s="33">
+        <v>8.49</v>
       </c>
     </row>
   </sheetData>
